--- a/Bewertung.xlsx
+++ b/Bewertung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucius.lechner/Documents/GitHub/PythonProgramm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496F7A81-3BD5-DB40-A886-E7653313ACDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57603F06-2324-8446-A936-88845A46281F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
